--- a/SRMS_V5_TEST_PACK/requirements_import.xlsx
+++ b/SRMS_V5_TEST_PACK/requirements_import.xlsx
@@ -461,12 +461,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="69" customWidth="1" min="1" max="1"/>
+    <col width="79" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SCHOOL REQUIREMENTS TEMPLATE</t>
+          <t>SCHOOL REQUIREMENTS TEMPLATE - EDGE CASES</t>
         </is>
       </c>
     </row>
@@ -501,21 +501,21 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1. Do not modify the column headers in Row 10.</t>
+          <t>1. Duplicate items are intentional.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2. Start data entry from Row 12 (below the sample row).</t>
+          <t>2. Blank quantity and very long item names are included to test resilience.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3. Ensure the 'Admission No' exists in the system where required.</t>
+          <t>3. Notes may be empty or contain punctuation.</t>
         </is>
       </c>
     </row>
@@ -557,90 +557,102 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ream Paper</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4</v>
+          <t>Reams of Paper</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Per Term</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laboratory Contribution</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4</v>
+          <t>Reams of Paper</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Per Term</t>
+          <t>Duplicate item to test overwrites in manual workflows</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Examination Fee</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
+          <t>Laboratory Contribution</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Per Term</t>
+          <t>For practical subjects</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Identity Card</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
+          <t>Examination Fee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Per Term</t>
+          <t>Mid-term collection</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sports Contribution</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
+          <t>Identity Cards</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Per Term</t>
+          <t>Bulk order</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Practical Fee</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
+          <t>Sports Contribution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Per Term</t>
+          <t>Includes jerseys and balls</t>
         </is>
       </c>
     </row>
@@ -650,14 +662,76 @@
           <t>School Development Fund</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>3</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Per Term</t>
-        </is>
-      </c>
+          <t>Long note with punctuation !@#</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Transport and Welfare</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zero quantity edge case</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Very Long Requirement Item Name Designed To Stretch The Column Width</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Long item name</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Blank Quantity Item</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quantity intentionally blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Optional Notes Item</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
